--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:50</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.95</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.27</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.64</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-17.97</v>
+        <v>-179.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:57</t>
+    <t xml:space="preserve">2026-10-02 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:33</t>
+    <t xml:space="preserve">2026-10-05 08:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
